--- a/EduAI_Task_Plan.WEEKLY.xlsx
+++ b/EduAI_Task_Plan.WEEKLY.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Weekly Summary" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Task Tracker'!$A$2:$F$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Task Tracker'!$A$2:$F$84</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="183">
   <si>
     <t>EduAI - Weekly Task Plan   |   Deadline 31 Aug 2026   |   Working days: Mon-Fri plus 2nd and 4th Saturdays.   Off: all Sundays, the 1st/3rd/5th Saturdays, and 15, 16, 23, 28, 29, 30 Aug.   |   All testing is scheduled last (27 and 31 Aug).</t>
   </si>
@@ -150,135 +150,126 @@
     <t>School onboarding - transactional and retry</t>
   </si>
   <si>
+    <t>Changed</t>
+  </si>
+  <si>
+    <t>13 Aug 2026: school, entitlements, auth user and profile are still separate writes with cleanup logic.</t>
+  </si>
+  <si>
+    <t>Entitlement limits and enforcement</t>
+  </si>
+  <si>
+    <t>13 Aug 2026: enforcement done (requireFeature + explicit ENTITLEMENTS_FAILURE_MODE). Seat/storage/AI limits not built.</t>
+  </si>
+  <si>
+    <t>Audit log viewer - filters and export</t>
+  </si>
+  <si>
+    <t>13 Aug 2026: filters by action/entity/actor/search + CSV export sharing the same query. /audit-log/actions supplies the vocabulary.</t>
+  </si>
+  <si>
+    <t>Cross-school lookup logging</t>
+  </si>
+  <si>
+    <t>13 Aug 2026: already shipped — student_directory.search is recorded with the query and result count.</t>
+  </si>
+  <si>
+    <t>Fri 14 Aug</t>
+  </si>
+  <si>
+    <t>School logo upload validation</t>
+  </si>
+  <si>
+    <t>13 Aug 2026: magic-byte sniffing (PNG/JPEG/WEBP) and declared MIME must match. Previously trusted client-supplied mimetype into a public bucket.</t>
+  </si>
+  <si>
+    <t>Pagination for schools and overview</t>
+  </si>
+  <si>
+    <t>13 Aug 2026: API paginated + searchable; overview counts moved to a SQL aggregate (was loading every user_profile). Pager UI on the Schools screen still to build.</t>
+  </si>
+  <si>
+    <t>3. Mail Providers (all modules)</t>
+  </si>
+  <si>
+    <t>Configure mail provider and templates</t>
+  </si>
+  <si>
+    <t>17 Aug 2026: SMTP transport + one template (school-admin welcome) exist. Remaining templates not built.</t>
+  </si>
+  <si>
+    <t>School onboarding welcome email</t>
+  </si>
+  <si>
+    <t>17 Aug 2026: already shipped — sendSchoolAdminWelcomeEmail fires on school creation and on adding an admin.</t>
+  </si>
+  <si>
+    <t>Week 2 (17-22 Aug)</t>
+  </si>
+  <si>
+    <t>Mon 17 Aug</t>
+  </si>
+  <si>
+    <t>Support ticket  - school admin</t>
+  </si>
+  <si>
+    <t>17 Aug 2026: not started.</t>
+  </si>
+  <si>
+    <t>Exam result and report notification</t>
+  </si>
+  <si>
     <t>Pending</t>
   </si>
   <si>
-    <t>13 Aug 2026: school, entitlements, auth user and profile are still separate writes with cleanup logic.</t>
-  </si>
-  <si>
-    <t>Entitlement limits and enforcement</t>
-  </si>
-  <si>
-    <t>13 Aug 2026: enforcement done (requireFeature + explicit ENTITLEMENTS_FAILURE_MODE). Seat/storage/AI limits not built.</t>
-  </si>
-  <si>
-    <t>Audit log viewer - filters and export</t>
-  </si>
-  <si>
-    <t>13 Aug 2026: filters by action/entity/actor/search + CSV export sharing the same query. /audit-log/actions supplies the vocabulary.</t>
-  </si>
-  <si>
-    <t>Cross-school lookup logging</t>
-  </si>
-  <si>
-    <t>13 Aug 2026: already shipped — student_directory.search is recorded with the query and result count.</t>
-  </si>
-  <si>
-    <t>Fri 14 Aug</t>
-  </si>
-  <si>
-    <t>School logo upload validation</t>
-  </si>
-  <si>
-    <t>13 Aug 2026: magic-byte sniffing (PNG/JPEG/WEBP) and declared MIME must match. Previously trusted client-supplied mimetype into a public bucket.</t>
-  </si>
-  <si>
-    <t>Pagination for schools and overview</t>
-  </si>
-  <si>
-    <t>13 Aug 2026: API paginated + searchable; overview counts moved to a SQL aggregate (was loading every user_profile). Pager UI on the Schools screen still to build.</t>
-  </si>
-  <si>
-    <t>3. Mail Providers (all modules)</t>
-  </si>
-  <si>
-    <t>Configure mail provider and templates</t>
+    <t>17 Aug 2026: not started. Result RELEASE control now exists, so a notification has a trigger to hang off.</t>
+  </si>
+  <si>
+    <t>Bounce and failure logging</t>
+  </si>
+  <si>
+    <t>17 Aug 2026: sendMail is fire-and-forget; failures are logged but not recorded per recipient.</t>
+  </si>
+  <si>
+    <t>4. Timetable and Lab</t>
+  </si>
+  <si>
+    <t>Conflict detection and clear messages</t>
+  </si>
+  <si>
+    <t>17 Aug 2026: already shipped — unique constraints on teacher/section/lab per period, mapped to plain-English messages, plus a lab seat-capacity warning.</t>
+  </si>
+  <si>
+    <t>Computer lab allocation</t>
+  </si>
+  <si>
+    <t>17 Aug 2026: already shipped — lab_id on timetable slots with capacity warning.</t>
+  </si>
+  <si>
+    <t>Link live session to timetable period</t>
+  </si>
+  <si>
+    <t>17 Aug 2026: live_sessions has no timetable_slot_id — sessions are not tied to a scheduled period.</t>
+  </si>
+  <si>
+    <t>Tue 18 Aug</t>
+  </si>
+  <si>
+    <t>Substitute teacher and rescheduling</t>
   </si>
   <si>
     <t>In progress</t>
   </si>
   <si>
-    <t>17 Aug 2026: SMTP transport + one template (school-admin welcome) exist. Remaining templates not built.</t>
-  </si>
-  <si>
-    <t>School onboarding welcome email</t>
-  </si>
-  <si>
-    <t>17 Aug 2026: already shipped — sendSchoolAdminWelcomeEmail fires on school creation and on adding an admin.</t>
-  </si>
-  <si>
-    <t>Week 2 (17-22 Aug)</t>
-  </si>
-  <si>
-    <t>Mon 17 Aug</t>
-  </si>
-  <si>
-    <t>Support ticket notification email</t>
-  </si>
-  <si>
-    <t>17 Aug 2026: not started.</t>
-  </si>
-  <si>
-    <t>Exam result and report notification</t>
-  </si>
-  <si>
-    <t>17 Aug 2026: not started. Result RELEASE control now exists, so a notification has a trigger to hang off.</t>
-  </si>
-  <si>
-    <t>Bounce and failure logging</t>
-  </si>
-  <si>
-    <t>17 Aug 2026: sendMail is fire-and-forget; failures are logged but not recorded per recipient.</t>
-  </si>
-  <si>
-    <t>4. Timetable and Lab</t>
-  </si>
-  <si>
-    <t>Conflict detection and clear messages</t>
-  </si>
-  <si>
-    <t>17 Aug 2026: already shipped — unique constraints on teacher/section/lab per period, mapped to plain-English messages, plus a lab seat-capacity warning.</t>
-  </si>
-  <si>
-    <t>Computer lab allocation</t>
-  </si>
-  <si>
-    <t>17 Aug 2026: already shipped — lab_id on timetable slots with capacity warning.</t>
-  </si>
-  <si>
-    <t>Link live session to timetable period</t>
-  </si>
-  <si>
-    <t>17 Aug 2026: live_sessions has no timetable_slot_id — sessions are not tied to a scheduled period.</t>
-  </si>
-  <si>
-    <t>Tue 18 Aug</t>
-  </si>
-  <si>
-    <t>Substitute teacher and rescheduling</t>
-  </si>
-  <si>
     <t>17 Aug 2026: rescheduling exists via timetable_exceptions. Substitute teacher not modelled.</t>
   </si>
   <si>
-    <t>Attendance recording</t>
-  </si>
-  <si>
-    <t>17 Aug 2026: session_participants records joins, but there is no attendance register or report.</t>
-  </si>
-  <si>
-    <t>Tablet usability fixes</t>
+    <t xml:space="preserve">bulk import </t>
   </si>
   <si>
     <t>5. Teacher</t>
   </si>
   <si>
-    <t>Exam builder - responsive form and validation</t>
-  </si>
-  <si>
-    <t>17 Aug 2026: server-side validation done; responsive pass not started.</t>
-  </si>
-  <si>
     <t>Exam publish - transactional and scope validation</t>
   </si>
   <si>
@@ -348,10 +339,13 @@
     <t>PIN login - roster search and duplicate names</t>
   </si>
   <si>
-    <t>Image based quizzes</t>
-  </si>
-  <si>
-    <t>Exam autosave, retry and offline indicator</t>
+    <t>Image based games</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exam </t>
+  </si>
+  <si>
+    <t>in progress</t>
   </si>
   <si>
     <t>Virtual lab UI improvements</t>
@@ -360,37 +354,31 @@
     <t>Fri 21 Aug</t>
   </si>
   <si>
-    <t>Exam submit confirmation and refresh recovery</t>
-  </si>
-  <si>
-    <t>Proper quizzes inside virtual labs</t>
+    <t xml:space="preserve">AI tutor - vision response </t>
   </si>
   <si>
     <t>AI chat - responsive and retry states</t>
   </si>
   <si>
-    <t>Today's Lab screen and period timer</t>
-  </si>
-  <si>
-    <t>Reconnect and shared computer handoff</t>
-  </si>
-  <si>
-    <t>Badges, streaks and challenge error states</t>
+    <t xml:space="preserve">Adding Redis to overall code </t>
+  </si>
+  <si>
+    <t>Badges, streaks and challenge error states- remove</t>
+  </si>
+  <si>
+    <t>done</t>
   </si>
   <si>
     <t>Sat 22 Aug</t>
   </si>
   <si>
-    <t>Reduced motion and low performance mode</t>
+    <t>UI changes</t>
   </si>
   <si>
     <t>7. Support Ticket</t>
   </si>
   <si>
-    <t>Ticket notifications</t>
-  </si>
-  <si>
-    <t>Attachment upload validation</t>
+    <t xml:space="preserve">only for school admin </t>
   </si>
   <si>
     <t>Role based ticket visibility</t>
@@ -604,7 +592,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -623,13 +611,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1118,148 +1099,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1666,7 +1647,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -2071,10 +2052,10 @@
         <v>53</v>
       </c>
       <c r="E21" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>54</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="22" ht="30" spans="1:6">
@@ -2088,18 +2069,18 @@
         <v>52</v>
       </c>
       <c r="D22" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" ht="18" customHeight="1" spans="1:6">
       <c r="A23" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -2109,22 +2090,22 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="C24" t="s">
         <v>52</v>
       </c>
       <c r="D24" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -2138,10 +2119,10 @@
         <v>52</v>
       </c>
       <c r="D25" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E25" s="11" t="s">
         <v>62</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>39</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>63</v>
@@ -2161,7 +2142,7 @@
         <v>64</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>65</v>
@@ -2221,7 +2202,7 @@
         <v>71</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>72</v>
@@ -2229,7 +2210,7 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>73</v>
@@ -2241,10 +2222,10 @@
         <v>74</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -2258,16 +2239,16 @@
         <v>66</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" ht="30" spans="1:6">
       <c r="A32" t="s">
         <v>13</v>
       </c>
@@ -2275,56 +2256,56 @@
         <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="D32" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" ht="30" spans="1:6">
+      <c r="A33" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" t="s">
         <v>78</v>
       </c>
-      <c r="E32" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" t="s">
-        <v>13</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C33" t="s">
-        <v>79</v>
-      </c>
       <c r="D33" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>39</v>
+        <v>81</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34" ht="30" spans="1:6">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="C34" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>11</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" ht="30" spans="1:6">
@@ -2335,36 +2316,36 @@
         <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>11</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" ht="30" spans="1:6">
       <c r="A36" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>11</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" ht="30" spans="1:6">
@@ -2375,16 +2356,16 @@
         <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>11</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38" ht="30" spans="1:6">
@@ -2395,19 +2376,19 @@
         <v>13</v>
       </c>
       <c r="C38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>11</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="39" ht="30" spans="1:6">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39" t="s">
         <v>13</v>
       </c>
@@ -2415,36 +2396,36 @@
         <v>13</v>
       </c>
       <c r="C39" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E39" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E39" s="11" t="s">
         <v>11</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40" ht="30" spans="1:6">
       <c r="A40" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="C40" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E40" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="E40" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -2455,36 +2436,36 @@
         <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="42" ht="30" spans="1:6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" t="s">
         <v>99</v>
       </c>
-      <c r="C42" t="s">
-        <v>79</v>
-      </c>
       <c r="D42" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="E42" s="9" t="s">
-        <v>54</v>
+        <v>101</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>11</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>101</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -2495,13 +2476,13 @@
         <v>13</v>
       </c>
       <c r="C43" t="s">
+        <v>99</v>
+      </c>
+      <c r="D43" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="D43" s="5" t="s">
-        <v>103</v>
-      </c>
       <c r="E43" s="11" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="F43" s="5" t="s">
         <v>13</v>
@@ -2515,13 +2496,13 @@
         <v>13</v>
       </c>
       <c r="C44" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D44" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E44" s="11" t="s">
         <v>104</v>
-      </c>
-      <c r="E44" s="11" t="s">
-        <v>39</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>13</v>
@@ -2535,13 +2516,13 @@
         <v>13</v>
       </c>
       <c r="C45" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>105</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="F45" s="5" t="s">
         <v>13</v>
@@ -2549,19 +2530,19 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="C46" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="F46" s="5" t="s">
         <v>13</v>
@@ -2575,13 +2556,13 @@
         <v>13</v>
       </c>
       <c r="C47" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>13</v>
@@ -2589,19 +2570,19 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>108</v>
+        <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>109</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>13</v>
@@ -2615,13 +2596,13 @@
         <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>110</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>39</v>
+        <v>111</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>13</v>
@@ -2629,19 +2610,19 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>13</v>
+        <v>112</v>
       </c>
       <c r="C50" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="F50" s="5" t="s">
         <v>13</v>
@@ -2655,13 +2636,13 @@
         <v>13</v>
       </c>
       <c r="C51" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="F51" s="5" t="s">
         <v>13</v>
@@ -2675,13 +2656,13 @@
         <v>13</v>
       </c>
       <c r="C52" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="F52" s="5" t="s">
         <v>13</v>
@@ -2695,13 +2676,13 @@
         <v>13</v>
       </c>
       <c r="C53" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="F53" s="5" t="s">
         <v>13</v>
@@ -2709,65 +2690,55 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>115</v>
+        <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>39</v>
+        <v>104</v>
       </c>
       <c r="F54" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
-      <c r="A55" t="s">
-        <v>13</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C55" t="s">
-        <v>117</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="E55" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="F55" s="5" t="s">
-        <v>13</v>
-      </c>
+    <row r="55" s="2" customFormat="1" ht="18" customHeight="1" spans="1:6">
+      <c r="A55" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="B55" s="8"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="8"/>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>13</v>
+        <v>119</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>13</v>
+        <v>120</v>
       </c>
       <c r="C56" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="E56" s="11" t="s">
-        <v>39</v>
+        <v>122</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="57" ht="30" spans="1:6">
       <c r="A57" t="s">
         <v>13</v>
       </c>
@@ -2775,19 +2746,19 @@
         <v>13</v>
       </c>
       <c r="C57" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="E57" s="11" t="s">
-        <v>39</v>
+        <v>124</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="58" ht="30" spans="1:6">
       <c r="A58" t="s">
         <v>13</v>
       </c>
@@ -2795,16 +2766,16 @@
         <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="E58" s="11" t="s">
-        <v>39</v>
+        <v>126</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>13</v>
+        <v>127</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -2815,69 +2786,79 @@
         <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="60" s="2" customFormat="1" ht="18" customHeight="1" spans="1:6">
-      <c r="A60" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="B60" s="8"/>
-      <c r="C60" s="8"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="8"/>
-    </row>
-    <row r="61" spans="1:6">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="60" ht="30" spans="1:6">
+      <c r="A60" t="s">
+        <v>13</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" t="s">
+        <v>121</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="E60" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="61" ht="30" spans="1:6">
       <c r="A61" t="s">
-        <v>123</v>
+        <v>13</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>124</v>
+        <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="E61" s="10" t="s">
-        <v>11</v>
+        <v>132</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>75</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="62" ht="30" spans="1:6">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="62" ht="45" spans="1:6">
       <c r="A62" t="s">
-        <v>13</v>
+        <v>119</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>13</v>
+        <v>134</v>
       </c>
       <c r="C62" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="E62" s="10" t="s">
-        <v>11</v>
+        <v>135</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>75</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="63" ht="30" spans="1:6">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
       <c r="A63" t="s">
         <v>13</v>
       </c>
@@ -2885,19 +2866,19 @@
         <v>13</v>
       </c>
       <c r="C63" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="E63" s="10" t="s">
-        <v>11</v>
+        <v>137</v>
+      </c>
+      <c r="E63" s="11" t="s">
+        <v>62</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="64" ht="45" spans="1:6">
       <c r="A64" t="s">
         <v>13</v>
       </c>
@@ -2905,19 +2886,19 @@
         <v>13</v>
       </c>
       <c r="C64" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="E64" s="11" t="s">
-        <v>39</v>
+        <v>138</v>
+      </c>
+      <c r="E64" s="9" t="s">
+        <v>75</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="65" ht="30" spans="1:6">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
       <c r="A65" t="s">
         <v>13</v>
       </c>
@@ -2925,19 +2906,19 @@
         <v>13</v>
       </c>
       <c r="C65" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="E65" s="10" t="s">
-        <v>11</v>
+        <v>140</v>
+      </c>
+      <c r="E65" s="11" t="s">
+        <v>62</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="66" ht="30" spans="1:6">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
       <c r="A66" t="s">
         <v>13</v>
       </c>
@@ -2945,59 +2926,59 @@
         <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="E66" s="9" t="s">
-        <v>54</v>
+        <v>141</v>
+      </c>
+      <c r="E66" s="11" t="s">
+        <v>62</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="67" ht="45" spans="1:6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>123</v>
+        <v>13</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>138</v>
+        <v>13</v>
       </c>
       <c r="C67" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="E67" s="9" t="s">
-        <v>54</v>
+        <v>142</v>
+      </c>
+      <c r="E67" s="11" t="s">
+        <v>62</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>140</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>13</v>
+        <v>119</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>13</v>
+        <v>143</v>
       </c>
       <c r="C68" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="69" ht="45" spans="1:6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
       <c r="A69" t="s">
         <v>13</v>
       </c>
@@ -3005,16 +2986,16 @@
         <v>13</v>
       </c>
       <c r="C69" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="E69" s="9" t="s">
-        <v>54</v>
+        <v>145</v>
+      </c>
+      <c r="E69" s="11" t="s">
+        <v>62</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>143</v>
+        <v>13</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -3025,16 +3006,16 @@
         <v>13</v>
       </c>
       <c r="C70" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>61</v>
+        <v>13</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -3045,13 +3026,13 @@
         <v>13</v>
       </c>
       <c r="C71" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F71" s="5" t="s">
         <v>13</v>
@@ -3065,13 +3046,13 @@
         <v>13</v>
       </c>
       <c r="C72" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F72" s="5" t="s">
         <v>13</v>
@@ -3079,19 +3060,19 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>123</v>
+        <v>13</v>
       </c>
       <c r="B73" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C73" t="s">
         <v>147</v>
       </c>
-      <c r="C73" t="s">
-        <v>125</v>
-      </c>
       <c r="D73" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F73" s="5" t="s">
         <v>13</v>
@@ -3099,22 +3080,22 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>13</v>
+        <v>119</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>13</v>
+        <v>151</v>
       </c>
       <c r="C74" t="s">
-        <v>125</v>
+        <v>9</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="E74" s="11" t="s">
-        <v>39</v>
+        <v>152</v>
+      </c>
+      <c r="E74" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>13</v>
+        <v>153</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -3125,19 +3106,19 @@
         <v>13</v>
       </c>
       <c r="C75" t="s">
-        <v>125</v>
+        <v>29</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="E75" s="11" t="s">
-        <v>39</v>
+        <v>154</v>
+      </c>
+      <c r="E75" s="9" t="s">
+        <v>75</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="76" ht="30" spans="1:6">
       <c r="A76" t="s">
         <v>13</v>
       </c>
@@ -3145,16 +3126,16 @@
         <v>13</v>
       </c>
       <c r="C76" t="s">
-        <v>151</v>
+        <v>52</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="E76" s="11" t="s">
-        <v>39</v>
+        <v>156</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>13</v>
+        <v>157</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -3165,16 +3146,16 @@
         <v>13</v>
       </c>
       <c r="C77" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="E77" s="11" t="s">
-        <v>39</v>
+        <v>158</v>
+      </c>
+      <c r="E77" s="9" t="s">
+        <v>75</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>13</v>
+        <v>159</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -3185,59 +3166,49 @@
         <v>13</v>
       </c>
       <c r="C78" t="s">
-        <v>151</v>
+        <v>78</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="E78" s="11" t="s">
-        <v>39</v>
+        <v>160</v>
+      </c>
+      <c r="E78" s="9" t="s">
+        <v>75</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79" t="s">
-        <v>123</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C79" t="s">
-        <v>9</v>
-      </c>
-      <c r="D79" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="E79" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F79" s="5" t="s">
-        <v>157</v>
-      </c>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="79" s="2" customFormat="1" ht="18" customHeight="1" spans="1:6">
+      <c r="A79" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="B79" s="8"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="8"/>
+      <c r="E79" s="8"/>
+      <c r="F79" s="8"/>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>13</v>
+        <v>162</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
       <c r="C80" t="s">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="81" ht="30" spans="1:6">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
       <c r="A81" t="s">
         <v>13</v>
       </c>
@@ -3245,16 +3216,16 @@
         <v>13</v>
       </c>
       <c r="C81" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="E81" s="10" t="s">
-        <v>11</v>
+        <v>166</v>
+      </c>
+      <c r="E81" s="11" t="s">
+        <v>62</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -3265,19 +3236,19 @@
         <v>13</v>
       </c>
       <c r="C82" t="s">
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="E82" s="9" t="s">
-        <v>54</v>
+        <v>168</v>
+      </c>
+      <c r="E82" s="11" t="s">
+        <v>62</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83" ht="30" spans="1:6">
       <c r="A83" t="s">
         <v>13</v>
       </c>
@@ -3285,138 +3256,48 @@
         <v>13</v>
       </c>
       <c r="C83" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="E83" s="9" t="s">
-        <v>54</v>
+        <v>169</v>
+      </c>
+      <c r="E83" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="84" s="2" customFormat="1" ht="18" customHeight="1" spans="1:6">
-      <c r="A84" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="B84" s="8"/>
-      <c r="C84" s="8"/>
-      <c r="D84" s="8"/>
-      <c r="E84" s="8"/>
-      <c r="F84" s="8"/>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85" t="s">
-        <v>166</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C85" t="s">
-        <v>79</v>
-      </c>
-      <c r="D85" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E85" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="F85" s="5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86" t="s">
-        <v>13</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C86" t="s">
-        <v>79</v>
-      </c>
-      <c r="D86" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="E86" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="F86" s="5" t="s">
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84" t="s">
+        <v>13</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C84" t="s">
+        <v>147</v>
+      </c>
+      <c r="D84" s="5" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87" t="s">
-        <v>13</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C87" t="s">
-        <v>117</v>
-      </c>
-      <c r="D87" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="E87" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="F87" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="88" ht="30" spans="1:6">
-      <c r="A88" t="s">
-        <v>13</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C88" t="s">
-        <v>125</v>
-      </c>
-      <c r="D88" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="E88" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89" t="s">
-        <v>13</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C89" t="s">
-        <v>151</v>
-      </c>
-      <c r="D89" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="E89" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="F89" s="5" t="s">
+      <c r="E84" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F84" s="5" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:F89" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:F84" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <mergeCells count="5">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A60:F60"/>
-    <mergeCell ref="A84:F84"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A79:F79"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
@@ -3444,25 +3325,25 @@
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3488,12 +3369,12 @@
         <v>2</v>
       </c>
       <c r="H2" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B3">
         <v>6</v>
@@ -3514,12 +3395,12 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B4">
         <v>4</v>
@@ -3540,12 +3421,12 @@
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -3566,12 +3447,12 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" spans="1:8">
       <c r="A6" s="4" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B6" s="4">
         <v>15</v>
@@ -3592,12 +3473,12 @@
         <v>2</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:8">
       <c r="A8" s="5" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>

--- a/EduAI_Task_Plan.WEEKLY.xlsx
+++ b/EduAI_Task_Plan.WEEKLY.xlsx
@@ -1,39 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2FBF3A5-E9AD-4690-928A-305A8204CA1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="25200" windowHeight="11730"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Task Tracker" sheetId="1" r:id="rId1"/>
     <sheet name="Weekly Summary" sheetId="2" r:id="rId2"/>
+    <sheet name="Additional Work Added" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Task Tracker'!$A$2:$F$84</definedName>
+    <definedName name="_xlnm._FilterDatabase">'Task Tracker'!$A$2:$F$83</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="183">
-  <si>
-    <t>EduAI - Weekly Task Plan   |   Deadline 31 Aug 2026   |   Working days: Mon-Fri plus 2nd and 4th Saturdays.   Off: all Sundays, the 1st/3rd/5th Saturdays, and 15, 16, 23, 28, 29, 30 Aug.   |   All testing is scheduled last (27 and 31 Aug).</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="232">
+  <si>
+    <t>EduAI - Weekly Task Plan   |   Deadline 7 Sep 2026 (revised from 31 Aug — see 'Additional Work Added')   |   Working days: Mon-Fri plus 2nd and 4th Saturdays.   Off: all Sundays, the 1st/3rd/5th Saturdays, and 15, 16, 23, 28, 29, 30 Aug.   |   All testing is scheduled last (27 Aug – 7 Sep).</t>
   </si>
   <si>
     <t>Week</t>
@@ -345,189 +334,186 @@
     <t xml:space="preserve">Exam </t>
   </si>
   <si>
+    <t>Virtual lab UI improvements</t>
+  </si>
+  <si>
+    <t>Fri 21 Aug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI tutor - vision response </t>
+  </si>
+  <si>
+    <t>AI chat - responsive and retry states</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adding Redis to overall code </t>
+  </si>
+  <si>
+    <t>Badges, streaks and challenge error states- remove</t>
+  </si>
+  <si>
+    <t>done</t>
+  </si>
+  <si>
+    <t>Sat 22 Aug</t>
+  </si>
+  <si>
+    <t>UI changes</t>
+  </si>
+  <si>
+    <t>7. Support Ticket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">only for school admin </t>
+  </si>
+  <si>
+    <t>Role based ticket visibility</t>
+  </si>
+  <si>
+    <t>Response time and SLA tracking</t>
+  </si>
+  <si>
+    <t>Error and empty states</t>
+  </si>
+  <si>
+    <t>Week 3 (24-27 Aug)</t>
+  </si>
+  <si>
+    <t>Mon 24 Aug</t>
+  </si>
+  <si>
+    <t>8. Platform and Security (all modules)</t>
+  </si>
+  <si>
+    <t>Repair build and dev environment</t>
+  </si>
+  <si>
+    <t>13 Aug 2026: both typechecks, both lints and the test suite are clean.</t>
+  </si>
+  <si>
+    <t>Test environment banner</t>
+  </si>
+  <si>
+    <t>13 Aug 2026: VITE_ENV_LABEL drives a banner on every page. Renders nothing in production by design.</t>
+  </si>
+  <si>
+    <t>Database access rules (RLS) rewrite</t>
+  </si>
+  <si>
+    <t>13 Aug 2026: writes revoked from authenticated + per-table policies; reads narrowed to teaching scope. Proven by regression (reopening a hole fails the suite).</t>
+  </si>
+  <si>
+    <t>Responsive portal shell</t>
+  </si>
+  <si>
+    <t>13 Aug 2026: not started.</t>
+  </si>
+  <si>
+    <t>API ownership checks</t>
+  </si>
+  <si>
+    <t>17 Aug 2026: every school-admin and teacher mutation re-reads the row scoped to the caller's school/ownership before writing. Verified a foreign id returns 404.</t>
+  </si>
+  <si>
+    <t>Tue 25 Aug</t>
+  </si>
+  <si>
+    <t>Session security on shared computers</t>
+  </si>
+  <si>
+    <t>17 Aug 2026: revocation repaired (it had never worked — signOut was being passed a user id, not a JWT) and 12h absolute expiry added. Tokens still in localStorage; no end-of-lab-period logout; no Super Admin MFA.</t>
+  </si>
+  <si>
+    <t>Shared dialogs and design components</t>
+  </si>
+  <si>
+    <t>Audit logging for sensitive actions</t>
+  </si>
+  <si>
+    <t>17 Aug 2026: credential resets, session revocation, account edits/deactivation, school suspension, entitlement changes (with before/after), result release. Imports, lab periods, content upload and exports still unlogged.</t>
+  </si>
+  <si>
+    <t>Accessibility - labels, text size, targets, tables</t>
+  </si>
+  <si>
+    <t>Rate limiting and PIN lockout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Done </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fonts and icons</t>
+  </si>
+  <si>
+    <t>Wed 26 Aug</t>
+  </si>
+  <si>
+    <t>Notifications and confirmations</t>
+  </si>
+  <si>
+    <t>Lazy loading and caching</t>
+  </si>
+  <si>
+    <t>Print and export layouts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDF simulator </t>
+  </si>
+  <si>
+    <t>Research</t>
+  </si>
+  <si>
+    <t>Bug Improvising</t>
+  </si>
+  <si>
+    <t>Integration</t>
+  </si>
+  <si>
+    <t>Thu 27 Aug</t>
+  </si>
+  <si>
+    <t>API testing - all school admin endpoints</t>
+  </si>
+  <si>
+    <t>13 Aug 2026: all 17 GET endpoints probed as School Admin; all 200 or correct 422 on missing params.</t>
+  </si>
+  <si>
+    <t>Module testing</t>
+  </si>
+  <si>
+    <t>13 Aug 2026: 42 security/isolation tests, hermetic and CI-ready. No functional/E2E suite yet.</t>
+  </si>
+  <si>
+    <t>Test with fictional recipients only</t>
+  </si>
+  <si>
+    <t>17 Aug 2026: all seeded addresses are @eduai.local / @sps.delhi.01.eduai.local — no real recipients exist in any environment.</t>
+  </si>
+  <si>
+    <t>Timetable CRUD testing</t>
+  </si>
+  <si>
+    <t>17 Aug 2026: endpoints exercised (slots, occurrences, exceptions). No automated suite.</t>
+  </si>
+  <si>
+    <t>CRUD operations testing</t>
+  </si>
+  <si>
+    <t>17 Aug 2026: exam CRUD now complete (create/edit/delete draft, publish, close). Not automated.</t>
+  </si>
+  <si>
+    <t>Week 4 (31 Aug)</t>
+  </si>
+  <si>
+    <t>Mon 31 Aug</t>
+  </si>
+  <si>
+    <t>AI feature testing - exam generator and grading</t>
+  </si>
+  <si>
     <t>in progress</t>
   </si>
   <si>
-    <t>Virtual lab UI improvements</t>
-  </si>
-  <si>
-    <t>Fri 21 Aug</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI tutor - vision response </t>
-  </si>
-  <si>
-    <t>AI chat - responsive and retry states</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adding Redis to overall code </t>
-  </si>
-  <si>
-    <t>Badges, streaks and challenge error states- remove</t>
-  </si>
-  <si>
-    <t>done</t>
-  </si>
-  <si>
-    <t>Sat 22 Aug</t>
-  </si>
-  <si>
-    <t>UI changes</t>
-  </si>
-  <si>
-    <t>7. Support Ticket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">only for school admin </t>
-  </si>
-  <si>
-    <t>Role based ticket visibility</t>
-  </si>
-  <si>
-    <t>Response time and SLA tracking</t>
-  </si>
-  <si>
-    <t>Error and empty states</t>
-  </si>
-  <si>
-    <t>Week 3 (24-27 Aug)</t>
-  </si>
-  <si>
-    <t>Mon 24 Aug</t>
-  </si>
-  <si>
-    <t>8. Platform and Security (all modules)</t>
-  </si>
-  <si>
-    <t>Repair build and dev environment</t>
-  </si>
-  <si>
-    <t>13 Aug 2026: both typechecks, both lints and the test suite are clean.</t>
-  </si>
-  <si>
-    <t>Test environment banner</t>
-  </si>
-  <si>
-    <t>13 Aug 2026: VITE_ENV_LABEL drives a banner on every page. Renders nothing in production by design.</t>
-  </si>
-  <si>
-    <t>Database access rules (RLS) rewrite</t>
-  </si>
-  <si>
-    <t>13 Aug 2026: writes revoked from authenticated + per-table policies; reads narrowed to teaching scope. Proven by regression (reopening a hole fails the suite).</t>
-  </si>
-  <si>
-    <t>Responsive portal shell</t>
-  </si>
-  <si>
-    <t>13 Aug 2026: not started.</t>
-  </si>
-  <si>
-    <t>API ownership checks</t>
-  </si>
-  <si>
-    <t>17 Aug 2026: every school-admin and teacher mutation re-reads the row scoped to the caller's school/ownership before writing. Verified a foreign id returns 404.</t>
-  </si>
-  <si>
-    <t>Public website - claims, mobile layout, demo form</t>
-  </si>
-  <si>
-    <t>17 Aug 2026: unbuilt-feature claims scrubbed from the landing page. Mobile layout and demo form outstanding.</t>
-  </si>
-  <si>
-    <t>Tue 25 Aug</t>
-  </si>
-  <si>
-    <t>Session security on shared computers</t>
-  </si>
-  <si>
-    <t>17 Aug 2026: revocation repaired (it had never worked — signOut was being passed a user id, not a JWT) and 12h absolute expiry added. Tokens still in localStorage; no end-of-lab-period logout; no Super Admin MFA.</t>
-  </si>
-  <si>
-    <t>Shared dialogs and design components</t>
-  </si>
-  <si>
-    <t>Audit logging for sensitive actions</t>
-  </si>
-  <si>
-    <t>17 Aug 2026: credential resets, session revocation, account edits/deactivation, school suspension, entitlement changes (with before/after), result release. Imports, lab periods, content upload and exports still unlogged.</t>
-  </si>
-  <si>
-    <t>Accessibility - labels, text size, targets, tables</t>
-  </si>
-  <si>
-    <t>Rate limiting and PIN lockout</t>
-  </si>
-  <si>
-    <t>Self-host fonts and icons</t>
-  </si>
-  <si>
-    <t>Wed 26 Aug</t>
-  </si>
-  <si>
-    <t>Notifications and confirmations</t>
-  </si>
-  <si>
-    <t>Lazy loading and caching</t>
-  </si>
-  <si>
-    <t>Print and export layouts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDF simulator </t>
-  </si>
-  <si>
-    <t>Research</t>
-  </si>
-  <si>
-    <t>Bug Improvising</t>
-  </si>
-  <si>
-    <t>Integration</t>
-  </si>
-  <si>
-    <t>Thu 27 Aug</t>
-  </si>
-  <si>
-    <t>API testing - all school admin endpoints</t>
-  </si>
-  <si>
-    <t>13 Aug 2026: all 17 GET endpoints probed as School Admin; all 200 or correct 422 on missing params.</t>
-  </si>
-  <si>
-    <t>Module testing</t>
-  </si>
-  <si>
-    <t>13 Aug 2026: 42 security/isolation tests, hermetic and CI-ready. No functional/E2E suite yet.</t>
-  </si>
-  <si>
-    <t>Test with fictional recipients only</t>
-  </si>
-  <si>
-    <t>17 Aug 2026: all seeded addresses are @eduai.local / @sps.delhi.01.eduai.local — no real recipients exist in any environment.</t>
-  </si>
-  <si>
-    <t>Timetable CRUD testing</t>
-  </si>
-  <si>
-    <t>17 Aug 2026: endpoints exercised (slots, occurrences, exceptions). No automated suite.</t>
-  </si>
-  <si>
-    <t>CRUD operations testing</t>
-  </si>
-  <si>
-    <t>17 Aug 2026: exam CRUD now complete (create/edit/delete draft, publish, close). Not automated.</t>
-  </si>
-  <si>
-    <t>Week 4 (31 Aug)</t>
-  </si>
-  <si>
-    <t>Mon 31 Aug</t>
-  </si>
-  <si>
-    <t>AI feature testing - exam generator and grading</t>
-  </si>
-  <si>
     <t>17 Aug 2026: generator and grading run; no evaluation harness for output quality.</t>
   </si>
   <si>
@@ -543,12 +529,75 @@
     <t>Tenant isolation testing</t>
   </si>
   <si>
+    <t xml:space="preserve">in progress </t>
+  </si>
+  <si>
     <t>17 Aug 2026: 20 hermetic tests — school A vs B, student A vs B, teacher vs untaught section, anonymous enumeration. Each negative paired with a control proving the row exists.</t>
   </si>
   <si>
     <t>Testing</t>
   </si>
   <si>
+    <t>Week 5 (1-7 Sep)</t>
+  </si>
+  <si>
+    <t>Tue 1 Sep</t>
+  </si>
+  <si>
+    <t>Regression testing — reader flow, Subjects → Chapters navigation, and the new simulation catalog</t>
+  </si>
+  <si>
+    <t>New scope — validates the PDF Simulator re-enable shipped this week (see 'Additional Work Added').</t>
+  </si>
+  <si>
+    <t>Exam Builder testing — class grouping, multi-section publish, live student attempt tracker</t>
+  </si>
+  <si>
+    <t>New scope — validates the rebuilt Create Exam workspace.</t>
+  </si>
+  <si>
+    <t>Wed 2 Sep</t>
+  </si>
+  <si>
+    <t>Academic Year Rollover testing — new section-change option during promotion</t>
+  </si>
+  <si>
+    <t>New scope — validates the promotion wizard change.</t>
+  </si>
+  <si>
+    <t>Continued from 31 Aug — closing out remaining isolation scenarios.</t>
+  </si>
+  <si>
+    <t>Thu 3 Sep</t>
+  </si>
+  <si>
+    <t>Continued from 31 Aug — no evaluation harness yet for output quality.</t>
+  </si>
+  <si>
+    <t>Continued from 31 Aug — still blocked on the import preview/duplicate-check fix (12 Aug).</t>
+  </si>
+  <si>
+    <t>Fri 4 Sep</t>
+  </si>
+  <si>
+    <t>Carried from 31 Aug, plus validates the new raise-ticket role restriction (teachers/school admins only).</t>
+  </si>
+  <si>
+    <t>Regression testing — sidebar, AI Doubt Tutor chat, cross-portal UI changes</t>
+  </si>
+  <si>
+    <t>New scope — validates this week's UI/UX polish (see 'Additional Work Added').</t>
+  </si>
+  <si>
+    <t>Mon 7 Sep</t>
+  </si>
+  <si>
+    <t>Final end-to-end / UAT pass before delivery sign-off</t>
+  </si>
+  <si>
+    <t>Covers Super Admin, School Admin, Teacher and Student portals.</t>
+  </si>
+  <si>
     <t>Working days</t>
   </si>
   <si>
@@ -580,22 +629,110 @@
   </si>
   <si>
     <t>How to use: on the Task Tracker sheet, filter by Week to report what closed and what is still open. Update the Progress column as you go. This summary is a snapshot taken when the file was generated and does not recalculate on its own.</t>
+  </si>
+  <si>
+    <t>EduAI — Additional Work Added (Unplanned Scope)   |   Original deadline: 31 Aug 2026   →   Revised delivery: 7 Sep 2026   |   The items below were completed this week outside the original Task Plan and are why delivery moved by 5 working days.   |   Extension working days: Tue 1 – Fri 4 Sep, then Mon 7 Sep. Sat 5 Sep (1st Saturday) and Sun 6 Sep are scheduled off-days under the existing working-day policy.</t>
+  </si>
+  <si>
+    <t>Timeline Impact</t>
+  </si>
+  <si>
+    <t>Original deadline: 31 Aug 2026 (Mon)</t>
+  </si>
+  <si>
+    <t>Revised delivery date: 7 Sep 2026 (Mon)</t>
+  </si>
+  <si>
+    <t>Additional working days used: 5 — Tue 1, Wed 2, Thu 3, Fri 4, Mon 7 Sep (Sat 5 &amp; Sun 6 Sep off per standing policy)</t>
+  </si>
+  <si>
+    <t>Reason: Unplanned additional scope completed this week — see the table below</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Additional Work Done</t>
+  </si>
+  <si>
+    <t>Why It Was Needed / Impact</t>
+  </si>
+  <si>
+    <t>27–28 Aug 2026</t>
+  </si>
+  <si>
+    <t>PDF Simulator &amp; Reader</t>
+  </si>
+  <si>
+    <t>Re-enabled the PDF Simulator across the Class 5-8 and 9-10 student portals — Subjects → Chapters → Reader navigation restored, ~150 new interactive simulations added (Physics, Chemistry, Biology, Math), and page-to-simulation matching switched from per-page AI review to a direct NCERT page-tag lookup.</t>
+  </si>
+  <si>
+    <t>This had been disabled earlier in the plan pending a decision; re-enabling it plus building out the simulation catalog was a full feature addition outside the original task list. The new tagging approach also cuts ongoing AI cost per upload. A new Super Admin 'Sim QA' tool was added so simulations can be spot-checked against their source pages before students see them.</t>
+  </si>
+  <si>
+    <t>28 Aug 2026</t>
+  </si>
+  <si>
+    <t>Environment / Release Readiness</t>
+  </si>
+  <si>
+    <t>Reconciled parallel work across two development setups into one consistent, tested codebase (PDF Simulator work merged with Academic Year Rollover / Student Directory work).</t>
+  </si>
+  <si>
+    <t>Necessary before either piece of work could safely ship — merging without this step risked silently losing one side’s changes. Verified with a full project type-check and lint pass, plus live login tests across all four portals (Super Admin, School Admin, Teacher, Student) after merging.</t>
+  </si>
+  <si>
+    <t>29–30 Aug 2026</t>
+  </si>
+  <si>
+    <t>Teacher – Exam Builder</t>
+  </si>
+  <si>
+    <t>Rebuilt the Create Exam workspace: exams grouped by class, one-click publish to every section with a shared exam window, a live per-student attempt tracker (not started / in progress / submitted) on each exam, and a students-reached column on the exam list. Removed the unused Question Bank browse panel and the Admit Card download feature.</t>
+  </si>
+  <si>
+    <t>Teachers had no way to see who had actually taken a published exam — the tracker closes that gap directly. Removing two unused features simplifies the page and cuts dead code (the Admit Card removal also dropped two now-unneeded backend dependencies).</t>
+  </si>
+  <si>
+    <t>30 Aug 2026</t>
+  </si>
+  <si>
+    <t>School Admin – Academic Year Rollover</t>
+  </si>
+  <si>
+    <t>Added the ability to change any section’s destination during promotion, not just sections with no matching name in the next class.</t>
+  </si>
+  <si>
+    <t>Sections don’t just carry the same name forward every year — schools reshuffle or merge them when students move up a class. The rollover wizard previously had no way to express that.</t>
+  </si>
+  <si>
+    <t>28–29 Aug 2026</t>
+  </si>
+  <si>
+    <t>Cross-Portal UI/UX</t>
+  </si>
+  <si>
+    <t>Visual and workflow polish across the sidebar, the AI Doubt Tutor chat, and the teacher dashboard; tightened who can raise a support ticket to teachers and school admins only.</t>
+  </si>
+  <si>
+    <t>General usability pass alongside the feature work above, plus a permissions correction that had been open.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -609,63 +746,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -673,94 +755,20 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -770,12 +778,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F2937"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE5E7EB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -805,192 +807,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFE5E7EB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFBFDBFE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF1F2937"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFE5E7EB"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -998,328 +835,66 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+  </cellStyleXfs>
+  <cellXfs count="23">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-  </cellStyleXfs>
-  <cellXfs count="13">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1641,100 +1216,100 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F84"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F93"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="3" max="3" width="31.109375" customWidth="1"/>
     <col min="4" max="4" width="52" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1" spans="1:6">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:6" ht="31.95" customHeight="1">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="20" customHeight="1" spans="1:6">
-      <c r="A2" s="7" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+    </row>
+    <row r="2" spans="1:6" s="1" customFormat="1" ht="19.95" customHeight="1">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="18" customHeight="1" spans="1:6">
-      <c r="A3" s="8" t="s">
+    <row r="3" spans="1:6" s="3" customFormat="1" ht="18" customHeight="1">
+      <c r="A3" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-    </row>
-    <row r="4" ht="30" spans="1:6">
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="5" t="s">
+      <c r="E4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" ht="30" spans="1:6">
+    <row r="5" spans="1:6" ht="28.8" customHeight="1">
       <c r="A5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="5" t="s">
+      <c r="E5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1742,19 +1317,19 @@
       <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="5" t="s">
+      <c r="E6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1762,19 +1337,19 @@
       <c r="A7" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C7" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="5" t="s">
+      <c r="E7" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1782,19 +1357,19 @@
       <c r="A8" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C8" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="5" t="s">
+      <c r="E8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1802,19 +1377,19 @@
       <c r="A9" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C9" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="5" t="s">
+      <c r="E9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1822,19 +1397,19 @@
       <c r="A10" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C10" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="5" t="s">
+      <c r="E10" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1842,19 +1417,19 @@
       <c r="A11" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C11" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="5" t="s">
+      <c r="E11" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1862,39 +1437,39 @@
       <c r="A12" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C12" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="5" t="s">
+      <c r="E12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="13" ht="30" spans="1:6">
+    <row r="13" spans="1:6" ht="28.8" customHeight="1">
       <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C13" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="4" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1902,19 +1477,19 @@
       <c r="A14" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C14" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="4" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1922,189 +1497,189 @@
       <c r="A15" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C15" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="16" ht="30" spans="1:6">
+    <row r="16" spans="1:6" ht="28.8" customHeight="1">
       <c r="A16" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C16" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="5" t="s">
+      <c r="E16" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="17" ht="30" spans="1:6">
+    <row r="17" spans="1:6" ht="28.8" customHeight="1">
       <c r="A17" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C17" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="5" t="s">
+      <c r="E17" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="18" ht="30" spans="1:6">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C18" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="5" t="s">
+      <c r="E18" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="19" ht="30" spans="1:6">
+    <row r="19" spans="1:6" ht="28.8" customHeight="1">
       <c r="A19" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C19" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E19" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="5" t="s">
+      <c r="E19" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="20" ht="30" spans="1:6">
+    <row r="20" spans="1:6" ht="28.8" customHeight="1">
       <c r="A20" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C20" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E20" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="5" t="s">
+      <c r="E20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="21" ht="30" spans="1:6">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C21" t="s">
         <v>52</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E21" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="5" t="s">
+      <c r="E21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="22" ht="30" spans="1:6">
+    <row r="22" spans="1:6" ht="28.8" customHeight="1">
       <c r="A22" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C22" t="s">
         <v>52</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E22" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="5" t="s">
+      <c r="E22" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="23" s="2" customFormat="1" ht="18" customHeight="1" spans="1:6">
-      <c r="A23" s="8" t="s">
+    <row r="23" spans="1:6" s="3" customFormat="1" ht="18" customHeight="1">
+      <c r="A23" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
         <v>57</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="3" t="s">
         <v>58</v>
       </c>
       <c r="C24" t="s">
         <v>52</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E24" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="5" t="s">
+      <c r="E24" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="4" t="s">
         <v>60</v>
       </c>
     </row>
@@ -2112,19 +1687,19 @@
       <c r="A25" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C25" t="s">
         <v>52</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E25" s="11" t="s">
+      <c r="E25" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="F25" s="4" t="s">
         <v>63</v>
       </c>
     </row>
@@ -2132,39 +1707,39 @@
       <c r="A26" t="s">
         <v>13</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C26" t="s">
         <v>52</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F26" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="27" ht="30" spans="1:6">
+    <row r="27" spans="1:6" ht="28.8" customHeight="1">
       <c r="A27" t="s">
         <v>13</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C27" t="s">
         <v>66</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E27" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="5" t="s">
+      <c r="E27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2172,19 +1747,19 @@
       <c r="A28" t="s">
         <v>13</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C28" t="s">
         <v>66</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E28" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="5" t="s">
+      <c r="E28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="4" t="s">
         <v>70</v>
       </c>
     </row>
@@ -2192,19 +1767,19 @@
       <c r="A29" t="s">
         <v>13</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C29" t="s">
         <v>66</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="E29" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="F29" s="4" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2212,19 +1787,19 @@
       <c r="A30" t="s">
         <v>57</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="3" t="s">
         <v>73</v>
       </c>
       <c r="C30" t="s">
         <v>66</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="E30" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="F30" s="4" t="s">
         <v>76</v>
       </c>
     </row>
@@ -2232,159 +1807,159 @@
       <c r="A31" t="s">
         <v>13</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C31" t="s">
         <v>66</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D31" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="E31" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" s="5" t="s">
+      <c r="E31" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="32" ht="30" spans="1:6">
+    <row r="32" spans="1:6" ht="28.8" customHeight="1">
       <c r="A32" t="s">
         <v>13</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C32" t="s">
         <v>78</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="E32" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="5" t="s">
+      <c r="E32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="33" ht="30" spans="1:6">
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
         <v>13</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C33" t="s">
         <v>78</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D33" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E33" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" s="5" t="s">
+      <c r="E33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="34" ht="30" spans="1:6">
+    <row r="34" spans="1:6" ht="28.8" customHeight="1">
       <c r="A34" t="s">
         <v>57</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="3" t="s">
         <v>83</v>
       </c>
       <c r="C34" t="s">
         <v>78</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D34" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="E34" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" s="5" t="s">
+      <c r="E34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="35" ht="30" spans="1:6">
+    <row r="35" spans="1:6" ht="28.8" customHeight="1">
       <c r="A35" t="s">
         <v>13</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C35" t="s">
         <v>78</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E35" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F35" s="5" t="s">
+      <c r="E35" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="4" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="36" ht="30" spans="1:6">
+    <row r="36" spans="1:6" ht="28.8" customHeight="1">
       <c r="A36" t="s">
         <v>13</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C36" t="s">
         <v>78</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E36" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F36" s="5" t="s">
+      <c r="E36" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="4" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="37" ht="30" spans="1:6">
+    <row r="37" spans="1:6" ht="28.8" customHeight="1">
       <c r="A37" t="s">
         <v>13</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C37" t="s">
         <v>78</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D37" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="E37" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F37" s="5" t="s">
+      <c r="E37" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="38" ht="30" spans="1:6">
+    <row r="38" spans="1:6" ht="28.8" customHeight="1">
       <c r="A38" t="s">
         <v>13</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C38" t="s">
         <v>78</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D38" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E38" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F38" s="5" t="s">
+      <c r="E38" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="4" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2392,39 +1967,39 @@
       <c r="A39" t="s">
         <v>13</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C39" t="s">
         <v>78</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D39" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E39" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F39" s="5" t="s">
+      <c r="E39" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" s="4" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="40" ht="30" spans="1:6">
+    <row r="40" spans="1:6" ht="28.8" customHeight="1">
       <c r="A40" t="s">
         <v>57</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="3" t="s">
         <v>96</v>
       </c>
       <c r="C40" t="s">
         <v>78</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="D40" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="E40" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F40" s="5" t="s">
+      <c r="E40" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="4" t="s">
         <v>98</v>
       </c>
     </row>
@@ -2432,19 +2007,19 @@
       <c r="A41" t="s">
         <v>13</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C41" t="s">
         <v>99</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="D41" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E41" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F41" s="5" t="s">
+      <c r="E41" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2452,19 +2027,19 @@
       <c r="A42" t="s">
         <v>13</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C42" t="s">
         <v>99</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D42" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E42" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F42" s="5" t="s">
+      <c r="E42" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2472,19 +2047,19 @@
       <c r="A43" t="s">
         <v>13</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C43" t="s">
         <v>99</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="D43" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E43" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F43" s="5" t="s">
+      <c r="E43" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2492,19 +2067,19 @@
       <c r="A44" t="s">
         <v>13</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C44" t="s">
         <v>99</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="D44" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E44" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="F44" s="5" t="s">
+      <c r="E44" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2512,19 +2087,19 @@
       <c r="A45" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C45" t="s">
         <v>99</v>
       </c>
-      <c r="D45" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="E45" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F45" s="5" t="s">
+      <c r="D45" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2532,19 +2107,19 @@
       <c r="A46" t="s">
         <v>57</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>106</v>
+      <c r="B46" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="C46" t="s">
         <v>99</v>
       </c>
-      <c r="D46" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E46" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F46" s="5" t="s">
+      <c r="D46" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2552,19 +2127,19 @@
       <c r="A47" t="s">
         <v>13</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C47" t="s">
         <v>99</v>
       </c>
-      <c r="D47" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="E47" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F47" s="5" t="s">
+      <c r="D47" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2572,19 +2147,19 @@
       <c r="A48" t="s">
         <v>13</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C48" t="s">
         <v>99</v>
       </c>
-      <c r="D48" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E48" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F48" s="5" t="s">
+      <c r="D48" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2592,19 +2167,19 @@
       <c r="A49" t="s">
         <v>13</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C49" t="s">
         <v>99</v>
       </c>
-      <c r="D49" s="5" t="s">
+      <c r="D49" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E49" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="E49" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="F49" s="5" t="s">
+      <c r="F49" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2612,19 +2187,19 @@
       <c r="A50" t="s">
         <v>57</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>112</v>
+      <c r="B50" s="3" t="s">
+        <v>111</v>
       </c>
       <c r="C50" t="s">
         <v>99</v>
       </c>
-      <c r="D50" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E50" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F50" s="5" t="s">
+      <c r="D50" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2632,19 +2207,19 @@
       <c r="A51" t="s">
         <v>13</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C51" t="s">
+        <v>113</v>
+      </c>
+      <c r="D51" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="D51" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="E51" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F51" s="5" t="s">
+      <c r="E51" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2652,19 +2227,19 @@
       <c r="A52" t="s">
         <v>13</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C52" t="s">
-        <v>114</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="E52" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F52" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F52" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2672,19 +2247,19 @@
       <c r="A53" t="s">
         <v>13</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C53" t="s">
-        <v>114</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="E53" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F53" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F53" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2692,289 +2267,286 @@
       <c r="A54" t="s">
         <v>13</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>114</v>
-      </c>
-      <c r="D54" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" s="3" customFormat="1" ht="18" customHeight="1">
+      <c r="A55" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="E54" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="F54" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="55" s="2" customFormat="1" ht="18" customHeight="1" spans="1:6">
-      <c r="A55" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="B55" s="8"/>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="8"/>
+      <c r="B55" s="17"/>
+      <c r="C55" s="17"/>
+      <c r="D55" s="17"/>
+      <c r="E55" s="17"/>
+      <c r="F55" s="17"/>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
+        <v>118</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="C56" t="s">
         <v>120</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="D56" s="5" t="s">
+      <c r="E56" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F56" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="E56" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F56" s="5" t="s">
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" t="s">
+        <v>13</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C57" t="s">
+        <v>120</v>
+      </c>
+      <c r="D57" s="4" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="57" ht="30" spans="1:6">
-      <c r="A57" t="s">
-        <v>13</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C57" t="s">
-        <v>121</v>
-      </c>
-      <c r="D57" s="5" t="s">
+      <c r="E57" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F57" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="E57" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F57" s="5" t="s">
+    </row>
+    <row r="58" spans="1:6" ht="28.8" customHeight="1">
+      <c r="A58" t="s">
+        <v>13</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C58" t="s">
+        <v>120</v>
+      </c>
+      <c r="D58" s="4" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="58" ht="30" spans="1:6">
-      <c r="A58" t="s">
-        <v>13</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C58" t="s">
-        <v>121</v>
-      </c>
-      <c r="D58" s="5" t="s">
+      <c r="E58" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F58" s="4" t="s">
         <v>126</v>
-      </c>
-      <c r="E58" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F58" s="5" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
         <v>13</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>121</v>
-      </c>
-      <c r="D59" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F59" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="E59" s="11" t="s">
+    </row>
+    <row r="60" spans="1:6" ht="28.8" customHeight="1">
+      <c r="A60" t="s">
+        <v>13</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" t="s">
+        <v>120</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="43.2" customHeight="1">
+      <c r="A61" t="s">
+        <v>118</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C61" t="s">
+        <v>120</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" t="s">
+        <v>13</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" t="s">
+        <v>120</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E62" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F59" s="5" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="60" ht="30" spans="1:6">
-      <c r="A60" t="s">
-        <v>13</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C60" t="s">
-        <v>121</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="E60" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F60" s="5" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="61" ht="30" spans="1:6">
-      <c r="A61" t="s">
-        <v>13</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" t="s">
-        <v>121</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="E61" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F61" s="5" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="62" ht="45" spans="1:6">
-      <c r="A62" t="s">
-        <v>119</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C62" t="s">
-        <v>121</v>
-      </c>
-      <c r="D62" s="5" t="s">
+      <c r="F62" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="43.2" customHeight="1">
+      <c r="A63" t="s">
+        <v>13</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" t="s">
+        <v>120</v>
+      </c>
+      <c r="D63" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="E62" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F62" s="5" t="s">
+      <c r="E63" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F63" s="4" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
-      <c r="A63" t="s">
-        <v>13</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" t="s">
-        <v>121</v>
-      </c>
-      <c r="D63" s="5" t="s">
+    <row r="64" spans="1:6">
+      <c r="A64" t="s">
+        <v>13</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" t="s">
+        <v>120</v>
+      </c>
+      <c r="D64" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="E63" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F63" s="5" t="s">
+      <c r="E64" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F64" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="64" ht="45" spans="1:6">
-      <c r="A64" t="s">
-        <v>13</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C64" t="s">
-        <v>121</v>
-      </c>
-      <c r="D64" s="5" t="s">
+    <row r="65" spans="1:6">
+      <c r="B65" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" t="s">
+        <v>120</v>
+      </c>
+      <c r="D65" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="E64" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F64" s="5" t="s">
+      <c r="E65" s="7" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65" t="s">
-        <v>13</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C65" t="s">
-        <v>121</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="E65" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F65" s="5" t="s">
-        <v>60</v>
+      <c r="F65" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
         <v>13</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B66" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>121</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="E66" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F66" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F66" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>13</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>13</v>
+        <v>118</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>141</v>
       </c>
       <c r="C67" t="s">
-        <v>121</v>
-      </c>
-      <c r="D67" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D67" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="E67" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F67" s="5" t="s">
+      <c r="E67" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F67" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>119</v>
-      </c>
-      <c r="B68" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C68" t="s">
+        <v>120</v>
+      </c>
+      <c r="D68" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="C68" t="s">
-        <v>121</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="E68" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F68" s="5" t="s">
+      <c r="E68" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F68" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2982,19 +2554,19 @@
       <c r="A69" t="s">
         <v>13</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="B69" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C69" t="s">
-        <v>121</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="E69" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F69" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F69" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3002,19 +2574,19 @@
       <c r="A70" t="s">
         <v>13</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B70" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C70" t="s">
-        <v>121</v>
-      </c>
-      <c r="D70" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D70" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="E70" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F70" s="5" t="s">
+      <c r="E70" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F70" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3022,19 +2594,19 @@
       <c r="A71" t="s">
         <v>13</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B71" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C71" t="s">
+        <v>145</v>
+      </c>
+      <c r="D71" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="D71" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="E71" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F71" s="5" t="s">
+      <c r="E71" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F71" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3042,99 +2614,99 @@
       <c r="A72" t="s">
         <v>13</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B72" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C72" t="s">
-        <v>147</v>
-      </c>
-      <c r="D72" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="E72" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F72" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F72" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>13</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>13</v>
+        <v>118</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>149</v>
       </c>
       <c r="C73" t="s">
-        <v>147</v>
-      </c>
-      <c r="D73" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D73" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="E73" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F73" s="5" t="s">
-        <v>13</v>
+      <c r="E73" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>119</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>151</v>
+        <v>13</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="C74" t="s">
-        <v>9</v>
-      </c>
-      <c r="D74" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D74" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="E74" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F74" s="5" t="s">
+      <c r="E74" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F74" s="4" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" ht="28.8" customHeight="1">
       <c r="A75" t="s">
         <v>13</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="B75" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C75" t="s">
-        <v>29</v>
-      </c>
-      <c r="D75" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D75" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="E75" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F75" s="5" t="s">
+      <c r="E75" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F75" s="4" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="76" ht="30" spans="1:6">
+    <row r="76" spans="1:6">
       <c r="A76" t="s">
         <v>13</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B76" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C76" t="s">
-        <v>52</v>
-      </c>
-      <c r="D76" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D76" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="E76" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F76" s="5" t="s">
+      <c r="E76" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F76" s="4" t="s">
         <v>157</v>
       </c>
     </row>
@@ -3142,174 +2714,325 @@
       <c r="A77" t="s">
         <v>13</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="B77" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C77" t="s">
-        <v>66</v>
-      </c>
-      <c r="D77" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="E77" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F77" s="5" t="s">
+      <c r="E77" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F77" s="4" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
-      <c r="A78" t="s">
-        <v>13</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C78" t="s">
+    <row r="78" spans="1:6" s="3" customFormat="1" ht="18" customHeight="1">
+      <c r="A78" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="B78" s="17"/>
+      <c r="C78" s="17"/>
+      <c r="D78" s="17"/>
+      <c r="E78" s="17"/>
+      <c r="F78" s="17"/>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" t="s">
+        <v>160</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C79" t="s">
         <v>78</v>
       </c>
-      <c r="D78" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="E78" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F78" s="5" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="79" s="2" customFormat="1" ht="18" customHeight="1" spans="1:6">
-      <c r="A79" s="8" t="s">
+      <c r="D79" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="B79" s="8"/>
-      <c r="C79" s="8"/>
-      <c r="D79" s="8"/>
-      <c r="E79" s="8"/>
-      <c r="F79" s="8"/>
+      <c r="E79" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>162</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>163</v>
+        <v>13</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="C80" t="s">
         <v>78</v>
       </c>
-      <c r="D80" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="E80" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F80" s="5" t="s">
+      <c r="D80" s="4" t="s">
         <v>165</v>
+      </c>
+      <c r="E80" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
         <v>13</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="B81" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C81" t="s">
+        <v>113</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="28.8" customHeight="1">
+      <c r="A82" t="s">
+        <v>13</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C82" t="s">
+        <v>120</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83" t="s">
+        <v>13</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C83" t="s">
+        <v>145</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="18" customHeight="1">
+      <c r="A84" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="B84" s="18"/>
+      <c r="C84" s="18"/>
+      <c r="D84" s="18"/>
+      <c r="E84" s="18"/>
+      <c r="F84" s="18"/>
+    </row>
+    <row r="85" spans="1:6" ht="28.8">
+      <c r="A85" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B85" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C85" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D85" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="E85" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F85" s="10" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="28.8">
+      <c r="A86" s="9"/>
+      <c r="B86" s="10"/>
+      <c r="C86" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="D81" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="E81" s="11" t="s">
+      <c r="D86" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E86" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="F81" s="5" t="s">
+      <c r="F86" s="10" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="28.8">
+      <c r="A87" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B87" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="C87" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D87" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="E87" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F87" s="10" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="28.8">
+      <c r="A88" s="9"/>
+      <c r="B88" s="10"/>
+      <c r="C88" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D88" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="E88" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F88" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B89" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="C89" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D89" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="E89" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F89" s="10" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" s="9"/>
+      <c r="B90" s="10"/>
+      <c r="C90" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D90" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="E90" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F90" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B91" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="C91" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="D91" s="11" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82" t="s">
-        <v>13</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C82" t="s">
-        <v>114</v>
-      </c>
-      <c r="D82" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E82" s="11" t="s">
+      <c r="E91" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="F82" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="83" ht="30" spans="1:6">
-      <c r="A83" t="s">
-        <v>13</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C83" t="s">
-        <v>121</v>
-      </c>
-      <c r="D83" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="E83" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F83" s="5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84" t="s">
-        <v>13</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C84" t="s">
-        <v>147</v>
-      </c>
-      <c r="D84" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="E84" s="11" t="s">
+      <c r="F91" s="10" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="28.8">
+      <c r="A92" s="9"/>
+      <c r="B92" s="10"/>
+      <c r="C92" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D92" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="E92" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="F84" s="5" t="s">
-        <v>13</v>
+      <c r="F92" s="10" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="28.8">
+      <c r="A93" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B93" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="C93" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D93" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="E93" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F93" s="10" t="s">
+        <v>191</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:F84" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
-  <mergeCells count="5">
+  <autoFilter ref="A2:F83" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <mergeCells count="6">
+    <mergeCell ref="A84:F84"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="A55:F55"/>
-    <mergeCell ref="A79:F79"/>
+    <mergeCell ref="A78:F78"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="7" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -3320,30 +3043,30 @@
     <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:8">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:8" s="1" customFormat="1">
+      <c r="A1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="B1" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>175</v>
+      <c r="G1" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3369,7 +3092,7 @@
         <v>2</v>
       </c>
       <c r="H2" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -3395,12 +3118,12 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B4">
         <v>4</v>
@@ -3421,12 +3144,12 @@
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -3447,53 +3170,209 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" spans="1:8">
-      <c r="A6" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="B6" s="4">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="3" customFormat="1">
+      <c r="A6" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="B6" s="13">
         <v>15</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="13">
         <v>88</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="13">
         <v>25</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="13">
         <v>15</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="13">
         <v>46</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="13">
         <v>2</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1" spans="1:8">
-      <c r="A8" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
+      <c r="H6" s="13" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="34.049999999999997" customHeight="1">
+      <c r="A8" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A8:H8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="52" customWidth="1"/>
+    <col min="4" max="4" width="62" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="48" customHeight="1">
+      <c r="A1" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+    </row>
+    <row r="3" spans="1:4" ht="19.95" customHeight="1">
+      <c r="A3" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+    </row>
+    <row r="4" spans="1:4" ht="16.05" customHeight="1">
+      <c r="A4" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+    </row>
+    <row r="5" spans="1:4" ht="16.05" customHeight="1">
+      <c r="A5" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+    </row>
+    <row r="6" spans="1:4" ht="16.05" customHeight="1">
+      <c r="A6" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+    </row>
+    <row r="7" spans="1:4" ht="18" customHeight="1">
+      <c r="A7" s="22" t="s">
+        <v>208</v>
+      </c>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+    </row>
+    <row r="9" spans="1:4" ht="19.95" customHeight="1">
+      <c r="A9" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="86.4">
+      <c r="A10" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="57.6">
+      <c r="A11" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="86.4">
+      <c r="A12" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="43.2">
+      <c r="A13" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="43.2">
+      <c r="A14" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>231</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A6:D6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>